--- a/rates/data/weekly-rates.xlsx
+++ b/rates/data/weekly-rates.xlsx
@@ -923,7 +923,7 @@
         <v>0.0315</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.0315</v>
+        <v>0.029</v>
       </c>
       <c r="P5" s="4" t="n">
         <v>0.029</v>
@@ -998,7 +998,7 @@
         <v>0.024</v>
       </c>
       <c r="AN5" s="4" t="n">
-        <v>0.024</v>
+        <v>0.0265</v>
       </c>
       <c r="AO5" s="4" t="n">
         <v>0.0265</v>
@@ -1035,7 +1035,7 @@
         <v>0.0005</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.0005</v>
+        <v>0.0025</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>0.0025</v>
@@ -1131,10 +1131,10 @@
         <v>0.01</v>
       </c>
       <c r="AO6" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0125</v>
       </c>
       <c r="AP6" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0125</v>
       </c>
       <c r="AQ6" s="4" t="n">
         <v>0.0125</v>

--- a/rates/data/weekly-rates.xlsx
+++ b/rates/data/weekly-rates.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ57"/>
+  <dimension ref="A1:AR57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -482,6 +482,7 @@
     <col width="11" customWidth="1" min="41" max="41"/>
     <col width="11" customWidth="1" min="42" max="42"/>
     <col width="11" customWidth="1" min="43" max="43"/>
+    <col width="11" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -619,6 +620,9 @@
       <c r="AQ2" s="2" t="n">
         <v>46297</v>
       </c>
+      <c r="AR2" s="2" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="inlineStr">
@@ -749,6 +753,9 @@
       <c r="AQ3" s="4" t="n">
         <v>0.03</v>
       </c>
+      <c r="AR3" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
@@ -879,6 +886,9 @@
       <c r="AQ4" s="4" t="n">
         <v>0.04</v>
       </c>
+      <c r="AR4" s="4" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
@@ -1009,6 +1019,9 @@
       <c r="AQ5" s="4" t="n">
         <v>0.0265</v>
       </c>
+      <c r="AR5" s="4" t="n">
+        <v>0.0265</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
@@ -1139,6 +1152,9 @@
       <c r="AQ6" s="4" t="n">
         <v>0.0125</v>
       </c>
+      <c r="AR6" s="4" t="n">
+        <v>0.0125</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
@@ -1269,6 +1285,9 @@
       <c r="AQ7" s="4" t="n">
         <v>0.03</v>
       </c>
+      <c r="AR7" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1404,6 +1423,9 @@
       <c r="AQ9" s="2" t="n">
         <v>46297</v>
       </c>
+      <c r="AR9" s="2" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
@@ -1535,6 +1557,9 @@
       <c r="AQ10" s="5" t="n">
         <v>0.03734</v>
       </c>
+      <c r="AR10" s="5" t="n">
+        <v>0.03741</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
@@ -1666,6 +1691,9 @@
       <c r="AQ11" s="5" t="n">
         <v>0.03937</v>
       </c>
+      <c r="AR11" s="5" t="n">
+        <v>0.03983</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
@@ -1797,6 +1825,9 @@
       <c r="AQ12" s="5" t="n">
         <v>0.04365</v>
       </c>
+      <c r="AR12" s="5" t="n">
+        <v>0.04395</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
@@ -1928,6 +1959,9 @@
       <c r="AQ13" s="4" t="n">
         <v>0.0446</v>
       </c>
+      <c r="AR13" s="4" t="n">
+        <v>0.0447</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
@@ -2059,6 +2093,9 @@
       <c r="AQ14" s="4" t="n">
         <v>0.0496</v>
       </c>
+      <c r="AR14" s="4" t="n">
+        <v>0.0489</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
@@ -2190,6 +2227,9 @@
       <c r="AQ15" s="4" t="n">
         <v>0.0528</v>
       </c>
+      <c r="AR15" s="4" t="n">
+        <v>0.0524</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2325,6 +2365,9 @@
       <c r="AQ17" s="2" t="n">
         <v>46297</v>
       </c>
+      <c r="AR17" s="2" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
@@ -2455,6 +2498,9 @@
       <c r="AQ18" s="5" t="n">
         <v>0.0305</v>
       </c>
+      <c r="AR18" s="5" t="n">
+        <v>0.02989</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
@@ -2586,6 +2632,9 @@
       <c r="AQ19" s="4" t="n">
         <v>0.0321</v>
       </c>
+      <c r="AR19" s="4" t="n">
+        <v>0.0324</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
@@ -2717,6 +2766,9 @@
       <c r="AQ20" s="4" t="n">
         <v>0.0318</v>
       </c>
+      <c r="AR20" s="4" t="n">
+        <v>0.0318</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2852,6 +2904,9 @@
       <c r="AQ22" s="2" t="n">
         <v>46297</v>
       </c>
+      <c r="AR22" s="2" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
@@ -2983,6 +3038,9 @@
       <c r="AQ23" s="5" t="n">
         <v>0.10442</v>
       </c>
+      <c r="AR23" s="5" t="n">
+        <v>0.10455</v>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
@@ -3114,6 +3172,9 @@
       <c r="AQ24" s="5" t="n">
         <v>0.04638</v>
       </c>
+      <c r="AR24" s="5" t="n">
+        <v>0.04651</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -3249,6 +3310,9 @@
       <c r="AQ26" s="2" t="n">
         <v>46297</v>
       </c>
+      <c r="AR26" s="2" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
@@ -3379,6 +3443,9 @@
       <c r="AQ27" s="5" t="n">
         <v>0.06211</v>
       </c>
+      <c r="AR27" s="5" t="n">
+        <v>0.06279</v>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="3" t="inlineStr">
@@ -3509,6 +3576,9 @@
       <c r="AQ28" s="5" t="n">
         <v>0.05438</v>
       </c>
+      <c r="AR28" s="5" t="n">
+        <v>0.05506</v>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="3" t="inlineStr">
@@ -3639,6 +3709,9 @@
       <c r="AQ29" s="5" t="n">
         <v>0.04655</v>
       </c>
+      <c r="AR29" s="5" t="n">
+        <v>0.04722</v>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="3" t="inlineStr">
@@ -3769,6 +3842,9 @@
       <c r="AQ30" s="5" t="n">
         <v>0.04504</v>
       </c>
+      <c r="AR30" s="5" t="n">
+        <v>0.04572</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -3911,6 +3987,9 @@
       <c r="AQ33" s="2" t="n">
         <v>46297</v>
       </c>
+      <c r="AR33" s="2" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="3" t="inlineStr">
@@ -4041,6 +4120,9 @@
       <c r="AQ34" s="4" t="n">
         <v>0.0636</v>
       </c>
+      <c r="AR34" s="4" t="n">
+        <v>0.0646</v>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="3" t="inlineStr">
@@ -4171,6 +4253,9 @@
       <c r="AQ35" s="4" t="n">
         <v>0.0377</v>
       </c>
+      <c r="AR35" s="4" t="n">
+        <v>0.0387</v>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="3" t="inlineStr">
@@ -4301,6 +4386,9 @@
       <c r="AQ36" s="4" t="n">
         <v>0.0368</v>
       </c>
+      <c r="AR36" s="4" t="n">
+        <v>0.0378</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -4436,6 +4524,9 @@
       <c r="AQ38" s="2" t="n">
         <v>46297</v>
       </c>
+      <c r="AR38" s="2" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="3" t="inlineStr">
@@ -4494,6 +4585,9 @@
       <c r="AQ39" s="4" t="n">
         <v>0.0373</v>
       </c>
+      <c r="AR39" s="4" t="n">
+        <v>0.0373</v>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="3" t="inlineStr">
@@ -4552,6 +4646,9 @@
       <c r="AQ40" s="4" t="n">
         <v>0.037</v>
       </c>
+      <c r="AR40" s="4" t="n">
+        <v>0.037</v>
+      </c>
     </row>
     <row r="41">
       <c r="B41" s="3" t="inlineStr">
@@ -4610,6 +4707,9 @@
       <c r="AQ41" s="4" t="n">
         <v>0.039</v>
       </c>
+      <c r="AR41" s="4" t="n">
+        <v>0.039</v>
+      </c>
     </row>
     <row r="42">
       <c r="B42" s="3" t="inlineStr">
@@ -4668,6 +4768,9 @@
       <c r="AQ42" s="4" t="n">
         <v>0.0365</v>
       </c>
+      <c r="AR42" s="4" t="n">
+        <v>0.0365</v>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="3" t="inlineStr">
@@ -4726,6 +4829,9 @@
       <c r="AQ43" s="4" t="n">
         <v>0.037</v>
       </c>
+      <c r="AR43" s="4" t="n">
+        <v>0.037</v>
+      </c>
     </row>
     <row r="44">
       <c r="B44" s="3" t="inlineStr">
@@ -4784,6 +4890,9 @@
       <c r="AQ44" s="4" t="n">
         <v>0.037</v>
       </c>
+      <c r="AR44" s="4" t="n">
+        <v>0.037</v>
+      </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
@@ -5316,6 +5425,9 @@
       <c r="AQ53" s="2" t="n">
         <v>46297</v>
       </c>
+      <c r="AR53" s="2" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
@@ -5446,6 +5558,9 @@
       <c r="AQ54" s="7" t="n">
         <v>1359.6</v>
       </c>
+      <c r="AR54" s="7" t="n">
+        <v>1339.2</v>
+      </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
@@ -5576,6 +5691,9 @@
       <c r="AQ55" s="8" t="n">
         <v>202.55</v>
       </c>
+      <c r="AR55" s="8" t="n">
+        <v>199.71</v>
+      </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
@@ -5706,6 +5824,9 @@
       <c r="AQ56" s="8" t="n">
         <v>860.3200000000001</v>
       </c>
+      <c r="AR56" s="8" t="n">
+        <v>847.46</v>
+      </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
@@ -5835,6 +5956,9 @@
       </c>
       <c r="AQ57" s="8" t="n">
         <v>1528.67</v>
+      </c>
+      <c r="AR57" s="8" t="n">
+        <v>1500.04</v>
       </c>
     </row>
   </sheetData>
